--- a/artfynd/A 57640-2024 artfynd.xlsx
+++ b/artfynd/A 57640-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031036</v>
+        <v>122031037</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704027</v>
+        <v>703886</v>
       </c>
       <c r="R2" t="n">
         <v>7115830</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031037</v>
+        <v>122031036</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703886</v>
+        <v>704027</v>
       </c>
       <c r="R3" t="n">
         <v>7115830</v>

--- a/artfynd/A 57640-2024 artfynd.xlsx
+++ b/artfynd/A 57640-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031037</v>
+        <v>122031036</v>
       </c>
       <c r="B2" t="n">
         <v>90807</v>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703886</v>
+        <v>704027</v>
       </c>
       <c r="R2" t="n">
         <v>7115830</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031036</v>
+        <v>122031037</v>
       </c>
       <c r="B3" t="n">
         <v>90807</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704027</v>
+        <v>703886</v>
       </c>
       <c r="R3" t="n">
         <v>7115830</v>

--- a/artfynd/A 57640-2024 artfynd.xlsx
+++ b/artfynd/A 57640-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031036</v>
+        <v>122031037</v>
       </c>
       <c r="B2" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704027</v>
+        <v>703886</v>
       </c>
       <c r="R2" t="n">
         <v>7115830</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122031037</v>
+        <v>122031036</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>90819</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703886</v>
+        <v>704027</v>
       </c>
       <c r="R3" t="n">
         <v>7115830</v>

--- a/artfynd/A 57640-2024 artfynd.xlsx
+++ b/artfynd/A 57640-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031037</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122031036</v>
       </c>
       <c r="B3" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
